--- a/diseases/d132/2015-2019.xlsx
+++ b/diseases/d132/2015-2019.xlsx
@@ -16157,9 +16157,6 @@
       <c r="O106" t="n">
         <v>0</v>
       </c>
-      <c r="Q106" t="n">
-        <v>0</v>
-      </c>
       <c r="R106" t="n">
         <v>0</v>
       </c>
@@ -16897,9 +16894,6 @@
       <c r="O111" t="n">
         <v>0</v>
       </c>
-      <c r="Q111" t="n">
-        <v>0</v>
-      </c>
       <c r="R111" t="n">
         <v>0</v>
       </c>
@@ -17637,9 +17631,6 @@
       <c r="O116" t="n">
         <v>0</v>
       </c>
-      <c r="Q116" t="n">
-        <v>0</v>
-      </c>
       <c r="R116" t="n">
         <v>0</v>
       </c>
@@ -18525,9 +18516,6 @@
       <c r="O122" t="n">
         <v>0</v>
       </c>
-      <c r="Q122" t="n">
-        <v>0</v>
-      </c>
       <c r="R122" t="n">
         <v>0</v>
       </c>
@@ -19265,9 +19253,6 @@
       <c r="O127" t="n">
         <v>0</v>
       </c>
-      <c r="Q127" t="n">
-        <v>0</v>
-      </c>
       <c r="R127" t="n">
         <v>0</v>
       </c>
@@ -20005,9 +19990,6 @@
       <c r="O132" t="n">
         <v>0</v>
       </c>
-      <c r="Q132" t="n">
-        <v>0</v>
-      </c>
       <c r="R132" t="n">
         <v>0</v>
       </c>
@@ -20893,9 +20875,6 @@
       <c r="O138" t="n">
         <v>0</v>
       </c>
-      <c r="Q138" t="n">
-        <v>0</v>
-      </c>
       <c r="R138" t="n">
         <v>0</v>
       </c>
@@ -21633,9 +21612,6 @@
       <c r="O143" t="n">
         <v>0</v>
       </c>
-      <c r="Q143" t="n">
-        <v>0</v>
-      </c>
       <c r="R143" t="n">
         <v>0</v>
       </c>
@@ -22521,9 +22497,6 @@
       <c r="O149" t="n">
         <v>0</v>
       </c>
-      <c r="Q149" t="n">
-        <v>0</v>
-      </c>
       <c r="R149" t="n">
         <v>0</v>
       </c>
@@ -23261,9 +23234,6 @@
       <c r="O154" t="n">
         <v>0</v>
       </c>
-      <c r="Q154" t="n">
-        <v>0</v>
-      </c>
       <c r="R154" t="n">
         <v>0</v>
       </c>
@@ -24001,9 +23971,6 @@
       <c r="O159" t="n">
         <v>0</v>
       </c>
-      <c r="Q159" t="n">
-        <v>0</v>
-      </c>
       <c r="R159" t="n">
         <v>0</v>
       </c>
@@ -24889,9 +24856,6 @@
       <c r="O165" t="n">
         <v>0</v>
       </c>
-      <c r="Q165" t="n">
-        <v>0</v>
-      </c>
       <c r="R165" t="n">
         <v>0</v>
       </c>
@@ -25629,9 +25593,6 @@
       <c r="O170" t="n">
         <v>0</v>
       </c>
-      <c r="Q170" t="n">
-        <v>0</v>
-      </c>
       <c r="R170" t="n">
         <v>0</v>
       </c>
@@ -26369,9 +26330,6 @@
       <c r="O175" t="n">
         <v>0</v>
       </c>
-      <c r="Q175" t="n">
-        <v>0</v>
-      </c>
       <c r="R175" t="n">
         <v>0</v>
       </c>
@@ -27109,9 +27067,6 @@
       <c r="O180" t="n">
         <v>0</v>
       </c>
-      <c r="Q180" t="n">
-        <v>0</v>
-      </c>
       <c r="R180" t="n">
         <v>0</v>
       </c>
@@ -27997,9 +27952,6 @@
       <c r="O186" t="n">
         <v>0</v>
       </c>
-      <c r="Q186" t="n">
-        <v>0</v>
-      </c>
       <c r="R186" t="n">
         <v>0</v>
       </c>
@@ -28737,9 +28689,6 @@
       <c r="O191" t="n">
         <v>0</v>
       </c>
-      <c r="Q191" t="n">
-        <v>0</v>
-      </c>
       <c r="R191" t="n">
         <v>0</v>
       </c>
@@ -29625,9 +29574,6 @@
       <c r="O197" t="n">
         <v>0</v>
       </c>
-      <c r="Q197" t="n">
-        <v>0</v>
-      </c>
       <c r="R197" t="n">
         <v>0</v>
       </c>
@@ -30365,9 +30311,6 @@
       <c r="O202" t="n">
         <v>0</v>
       </c>
-      <c r="Q202" t="n">
-        <v>0</v>
-      </c>
       <c r="R202" t="n">
         <v>0</v>
       </c>
@@ -31105,9 +31048,6 @@
       <c r="O207" t="n">
         <v>0</v>
       </c>
-      <c r="Q207" t="n">
-        <v>0</v>
-      </c>
       <c r="R207" t="n">
         <v>0</v>
       </c>
@@ -31993,9 +31933,6 @@
       <c r="O213" t="n">
         <v>0</v>
       </c>
-      <c r="Q213" t="n">
-        <v>0</v>
-      </c>
       <c r="R213" t="n">
         <v>0</v>
       </c>
@@ -32733,9 +32670,6 @@
       <c r="O218" t="n">
         <v>0</v>
       </c>
-      <c r="Q218" t="n">
-        <v>0</v>
-      </c>
       <c r="R218" t="n">
         <v>0</v>
       </c>
@@ -33473,9 +33407,6 @@
       <c r="O223" t="n">
         <v>0</v>
       </c>
-      <c r="Q223" t="n">
-        <v>0</v>
-      </c>
       <c r="R223" t="n">
         <v>0</v>
       </c>
@@ -34361,9 +34292,6 @@
       <c r="O229" t="n">
         <v>0</v>
       </c>
-      <c r="Q229" t="n">
-        <v>0</v>
-      </c>
       <c r="R229" t="n">
         <v>0</v>
       </c>
@@ -35101,9 +35029,6 @@
       <c r="O234" t="n">
         <v>0</v>
       </c>
-      <c r="Q234" t="n">
-        <v>0</v>
-      </c>
       <c r="R234" t="n">
         <v>0</v>
       </c>
@@ -35989,9 +35914,6 @@
       <c r="O240" t="n">
         <v>0</v>
       </c>
-      <c r="Q240" t="n">
-        <v>0</v>
-      </c>
       <c r="R240" t="n">
         <v>0</v>
       </c>
@@ -36729,9 +36651,6 @@
       <c r="O245" t="n">
         <v>0</v>
       </c>
-      <c r="Q245" t="n">
-        <v>0</v>
-      </c>
       <c r="R245" t="n">
         <v>0</v>
       </c>
@@ -37469,9 +37388,6 @@
       <c r="O250" t="n">
         <v>0</v>
       </c>
-      <c r="Q250" t="n">
-        <v>0</v>
-      </c>
       <c r="R250" t="n">
         <v>0</v>
       </c>
@@ -38209,9 +38125,6 @@
       <c r="O255" t="n">
         <v>0</v>
       </c>
-      <c r="Q255" t="n">
-        <v>0</v>
-      </c>
       <c r="R255" t="n">
         <v>0</v>
       </c>
@@ -39097,9 +39010,6 @@
       <c r="O261" t="n">
         <v>0</v>
       </c>
-      <c r="Q261" t="n">
-        <v>0</v>
-      </c>
       <c r="R261" t="n">
         <v>0</v>
       </c>
@@ -39837,9 +39747,6 @@
       <c r="O266" t="n">
         <v>1</v>
       </c>
-      <c r="Q266" t="n">
-        <v>0</v>
-      </c>
       <c r="R266" t="n">
         <v>0.001931701002201251</v>
       </c>
@@ -40577,9 +40484,6 @@
       <c r="O271" t="n">
         <v>0</v>
       </c>
-      <c r="Q271" t="n">
-        <v>0</v>
-      </c>
       <c r="R271" t="n">
         <v>0</v>
       </c>
@@ -41465,9 +41369,6 @@
       <c r="O277" t="n">
         <v>1</v>
       </c>
-      <c r="Q277" t="n">
-        <v>0</v>
-      </c>
       <c r="R277" t="n">
         <v>0.001931701002201251</v>
       </c>
@@ -42205,9 +42106,6 @@
       <c r="O282" t="n">
         <v>0</v>
       </c>
-      <c r="Q282" t="n">
-        <v>0</v>
-      </c>
       <c r="R282" t="n">
         <v>0</v>
       </c>
@@ -43093,9 +42991,6 @@
       <c r="O288" t="n">
         <v>1</v>
       </c>
-      <c r="Q288" t="n">
-        <v>0</v>
-      </c>
       <c r="R288" t="n">
         <v>0.001931701002201251</v>
       </c>
@@ -43831,9 +43726,6 @@
         <v>0</v>
       </c>
       <c r="O293" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q293" t="n">
         <v>0</v>
       </c>
       <c r="R293" t="n">
